--- a/grupos/6ARHM - Estadisticos 20232.xlsx
+++ b/grupos/6ARHM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="67">
   <si>
     <t>Materia</t>
   </si>
@@ -188,18 +188,18 @@
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
+    <t>Martínez Marañon Mauricio</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
+    <t>Velasco Sánchez David</t>
+  </si>
+  <si>
     <t>Ochoa Martínez Mayeli</t>
   </si>
   <si>
-    <t>Martínez Marañon Mauricio</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Velasco Sánchez David</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,19 +215,10 @@
     <t>IXMATLAHUA</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>PORTILLA</t>
-  </si>
-  <si>
     <t>LIZBETH JOSELYN</t>
-  </si>
-  <si>
-    <t>GETSEMANI GUADALUPE</t>
   </si>
 </sst>
 </file>
@@ -738,19 +729,19 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -786,7 +777,7 @@
         <v>10</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -815,19 +806,19 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -857,7 +848,7 @@
         <v>10</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -892,19 +883,19 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -969,19 +960,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1008,16 +999,16 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W7">
         <v>8</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1046,19 +1037,19 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1082,7 +1073,7 @@
         <v>9</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1094,7 +1085,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1123,19 +1114,19 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1162,16 +1153,16 @@
         <v>9</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>8</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1200,19 +1191,19 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1239,13 +1230,13 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>10</v>
@@ -1277,19 +1268,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1313,7 +1304,7 @@
         <v>10</v>
       </c>
       <c r="U11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1325,7 +1316,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1354,19 +1345,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1390,19 +1381,19 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1431,19 +1422,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1467,19 +1458,19 @@
         <v>9</v>
       </c>
       <c r="U13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X13">
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1508,19 +1499,19 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1544,7 +1535,7 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>7</v>
@@ -1553,10 +1544,10 @@
         <v>8</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1585,19 +1576,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1662,19 +1653,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1704,13 +1695,13 @@
         <v>7</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1739,19 +1730,19 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1781,7 +1772,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>7</v>
@@ -1816,19 +1807,19 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1852,13 +1843,13 @@
         <v>10</v>
       </c>
       <c r="U18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>9</v>
       </c>
       <c r="W18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -1893,19 +1884,19 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -1929,19 +1920,19 @@
         <v>10</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -1970,19 +1961,19 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2047,19 +2038,19 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2083,16 +2074,16 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>9</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2124,19 +2115,19 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2163,16 +2154,16 @@
         <v>8</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2201,19 +2192,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2240,16 +2231,16 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2278,19 +2269,19 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2314,7 +2305,7 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2326,7 +2317,7 @@
         <v>8</v>
       </c>
       <c r="Y24">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2355,19 +2346,19 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2391,10 +2382,10 @@
         <v>9</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W25">
         <v>9</v>
@@ -2403,7 +2394,7 @@
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2432,19 +2423,19 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2468,7 +2459,7 @@
         <v>10</v>
       </c>
       <c r="U26">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>10</v>
@@ -2509,19 +2500,19 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2545,19 +2536,19 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2586,19 +2577,19 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2622,7 +2613,7 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>10</v>
@@ -2634,7 +2625,7 @@
         <v>10</v>
       </c>
       <c r="Y28">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2663,19 +2654,19 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2699,19 +2690,19 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>8</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X29">
         <v>8</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2740,19 +2731,19 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2779,7 +2770,7 @@
         <v>9</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>9</v>
@@ -2817,19 +2808,19 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -2865,7 +2856,7 @@
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2894,19 +2885,19 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -2930,7 +2921,7 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -2971,19 +2962,19 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3013,13 +3004,13 @@
         <v>7</v>
       </c>
       <c r="W33">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3048,19 +3039,19 @@
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3084,19 +3075,19 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X34">
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3356,7 +3347,7 @@
         <v>100</v>
       </c>
       <c r="J6">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K6">
         <v>100</v>
@@ -3365,7 +3356,7 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>93.3</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -3374,7 +3365,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3383,7 +3374,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>93.3</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3415,34 +3406,34 @@
         <v>100</v>
       </c>
       <c r="J7">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L7">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="M7">
+        <v>98.2</v>
+      </c>
+      <c r="N7">
+        <v>100</v>
+      </c>
+      <c r="O7">
+        <v>100</v>
+      </c>
+      <c r="P7">
+        <v>92.3</v>
+      </c>
+      <c r="Q7">
         <v>96.7</v>
       </c>
-      <c r="N7">
-        <v>100</v>
-      </c>
-      <c r="O7">
-        <v>100</v>
-      </c>
-      <c r="P7">
-        <v>88.5</v>
-      </c>
-      <c r="Q7">
-        <v>100</v>
-      </c>
       <c r="R7">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="S7">
-        <v>96.7</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3474,16 +3465,16 @@
         <v>100</v>
       </c>
       <c r="J8">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N8">
         <v>80</v>
@@ -3492,16 +3483,16 @@
         <v>100</v>
       </c>
       <c r="P8">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q8">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>90</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3533,34 +3524,34 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L9">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="M9">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9">
+        <v>100</v>
+      </c>
+      <c r="P9">
+        <v>96.2</v>
+      </c>
+      <c r="Q9">
         <v>96.7</v>
       </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
-      <c r="O9">
-        <v>100</v>
-      </c>
-      <c r="P9">
-        <v>92.3</v>
-      </c>
-      <c r="Q9">
-        <v>100</v>
-      </c>
       <c r="R9">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="S9">
-        <v>96.7</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3592,13 +3583,13 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="K10">
         <v>100</v>
       </c>
       <c r="L10">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M10">
         <v>100</v>
@@ -3610,13 +3601,13 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="Q10">
         <v>100</v>
       </c>
       <c r="R10">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S10">
         <v>100</v>
@@ -3651,34 +3642,34 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>100</v>
+        <v>94.2</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L11">
         <v>100</v>
       </c>
       <c r="M11">
+        <v>94.5</v>
+      </c>
+      <c r="N11">
+        <v>100</v>
+      </c>
+      <c r="O11">
+        <v>100</v>
+      </c>
+      <c r="P11">
+        <v>94.2</v>
+      </c>
+      <c r="Q11">
         <v>96.7</v>
       </c>
-      <c r="N11">
-        <v>100</v>
-      </c>
-      <c r="O11">
-        <v>100</v>
-      </c>
-      <c r="P11">
-        <v>100</v>
-      </c>
-      <c r="Q11">
-        <v>100</v>
-      </c>
       <c r="R11">
         <v>100</v>
       </c>
       <c r="S11">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3710,16 +3701,16 @@
         <v>100</v>
       </c>
       <c r="J12">
-        <v>100</v>
+        <v>94.2</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L12">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N12">
         <v>100</v>
@@ -3728,16 +3719,16 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>94.2</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R12">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S12">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3769,16 +3760,16 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N13">
         <v>100</v>
@@ -3787,16 +3778,16 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q13">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R13">
         <v>100</v>
       </c>
       <c r="S13">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3831,13 +3822,13 @@
         <v>88.5</v>
       </c>
       <c r="K14">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="L14">
         <v>100</v>
       </c>
       <c r="M14">
-        <v>96.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N14">
         <v>100</v>
@@ -3849,13 +3840,13 @@
         <v>88.5</v>
       </c>
       <c r="Q14">
-        <v>93.3</v>
+        <v>90</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>96.7</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3887,7 +3878,7 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K15">
         <v>100</v>
@@ -3905,7 +3896,7 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -3946,10 +3937,10 @@
         <v>100</v>
       </c>
       <c r="J16">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -3964,10 +3955,10 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q16">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -4005,16 +3996,16 @@
         <v>100</v>
       </c>
       <c r="J17">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="K17">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M17">
-        <v>86.7</v>
+        <v>80</v>
       </c>
       <c r="N17">
         <v>80</v>
@@ -4023,16 +4014,16 @@
         <v>100</v>
       </c>
       <c r="P17">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="Q17">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="R17">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S17">
-        <v>86.7</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4064,7 +4055,7 @@
         <v>100</v>
       </c>
       <c r="J18">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K18">
         <v>100</v>
@@ -4073,7 +4064,7 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N18">
         <v>100</v>
@@ -4082,7 +4073,7 @@
         <v>100</v>
       </c>
       <c r="P18">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q18">
         <v>100</v>
@@ -4091,7 +4082,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4123,10 +4114,10 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>92.3</v>
+        <v>94.2</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -4141,10 +4132,10 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>92.3</v>
+        <v>94.2</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4182,7 +4173,7 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K20">
         <v>100</v>
@@ -4200,7 +4191,7 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="Q20">
         <v>100</v>
@@ -4241,16 +4232,16 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="K21">
         <v>93.3</v>
       </c>
       <c r="L21">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="M21">
-        <v>100</v>
+        <v>92.7</v>
       </c>
       <c r="N21">
         <v>100</v>
@@ -4259,16 +4250,16 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="Q21">
         <v>93.3</v>
       </c>
       <c r="R21">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="S21">
-        <v>100</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4300,16 +4291,16 @@
         <v>100</v>
       </c>
       <c r="J22">
+        <v>86.5</v>
+      </c>
+      <c r="K22">
+        <v>93.3</v>
+      </c>
+      <c r="L22">
         <v>88.5</v>
       </c>
-      <c r="K22">
-        <v>100</v>
-      </c>
-      <c r="L22">
-        <v>84.59999999999999</v>
-      </c>
       <c r="M22">
-        <v>83.3</v>
+        <v>87.3</v>
       </c>
       <c r="N22">
         <v>100</v>
@@ -4318,16 +4309,16 @@
         <v>100</v>
       </c>
       <c r="P22">
+        <v>86.5</v>
+      </c>
+      <c r="Q22">
+        <v>93.3</v>
+      </c>
+      <c r="R22">
         <v>88.5</v>
       </c>
-      <c r="Q22">
-        <v>100</v>
-      </c>
-      <c r="R22">
-        <v>84.59999999999999</v>
-      </c>
       <c r="S22">
-        <v>83.3</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4359,16 +4350,16 @@
         <v>100</v>
       </c>
       <c r="J23">
-        <v>92.3</v>
+        <v>94.2</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L23">
         <v>96.2</v>
       </c>
       <c r="M23">
-        <v>96.7</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -4377,16 +4368,16 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>92.3</v>
+        <v>94.2</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="R23">
         <v>96.2</v>
       </c>
       <c r="S23">
-        <v>96.7</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4418,16 +4409,16 @@
         <v>100</v>
       </c>
       <c r="J24">
-        <v>96.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
       <c r="N24">
         <v>80</v>
@@ -4436,16 +4427,16 @@
         <v>100</v>
       </c>
       <c r="P24">
-        <v>96.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="Q24">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R24">
         <v>100</v>
       </c>
       <c r="S24">
-        <v>96.7</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4598,13 +4589,13 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="N27">
         <v>80</v>
@@ -4616,13 +4607,13 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>100</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4660,10 +4651,10 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M28">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -4678,10 +4669,10 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="S28">
-        <v>100</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4713,16 +4704,16 @@
         <v>100</v>
       </c>
       <c r="J29">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="K29">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>100</v>
+        <v>85.5</v>
       </c>
       <c r="N29">
         <v>100</v>
@@ -4731,16 +4722,16 @@
         <v>100</v>
       </c>
       <c r="P29">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="Q29">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="R29">
         <v>100</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4772,13 +4763,13 @@
         <v>100</v>
       </c>
       <c r="J30">
-        <v>88.5</v>
+        <v>94.2</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L30">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="M30">
         <v>100</v>
@@ -4790,13 +4781,13 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>88.5</v>
+        <v>94.2</v>
       </c>
       <c r="Q30">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="R30">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="S30">
         <v>100</v>
@@ -4834,7 +4825,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -4852,7 +4843,7 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -4890,16 +4881,16 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="K32">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L32">
         <v>100</v>
       </c>
       <c r="M32">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="N32">
         <v>100</v>
@@ -4908,16 +4899,16 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="Q32">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="R32">
         <v>100</v>
       </c>
       <c r="S32">
-        <v>100</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -4949,16 +4940,16 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>88.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>86.5</v>
       </c>
       <c r="M33">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N33">
         <v>100</v>
@@ -4967,16 +4958,16 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>88.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="Q33">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="R33">
-        <v>100</v>
+        <v>86.5</v>
       </c>
       <c r="S33">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5008,7 +4999,7 @@
         <v>100</v>
       </c>
       <c r="J34">
-        <v>92.3</v>
+        <v>94.2</v>
       </c>
       <c r="K34">
         <v>100</v>
@@ -5017,7 +5008,7 @@
         <v>100</v>
       </c>
       <c r="M34">
-        <v>100</v>
+        <v>92.7</v>
       </c>
       <c r="N34">
         <v>80</v>
@@ -5026,7 +5017,7 @@
         <v>100</v>
       </c>
       <c r="P34">
-        <v>92.3</v>
+        <v>94.2</v>
       </c>
       <c r="Q34">
         <v>100</v>
@@ -5035,7 +5026,7 @@
         <v>100</v>
       </c>
       <c r="S34">
-        <v>100</v>
+        <v>92.7</v>
       </c>
     </row>
   </sheetData>
@@ -5113,7 +5104,7 @@
         <v>3.2</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5124,7 +5115,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -5133,19 +5124,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F3" s="2">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="G3" s="2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>9.1</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5156,7 +5147,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -5177,7 +5168,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.1</v>
+        <v>9.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5188,7 +5179,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -5209,7 +5200,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5220,10 +5211,10 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C6">
         <v>31</v>
@@ -5241,7 +5232,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.6</v>
+        <v>8.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5252,10 +5243,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C7">
         <v>31</v>
@@ -5273,7 +5264,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.9</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5323,7 +5314,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5361,10 +5352,10 @@
         <v>64</v>
       </c>
       <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
         <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>68</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -5373,29 +5364,6 @@
         <v>55</v>
       </c>
       <c r="G2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920250</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G3">
         <v>5</v>
       </c>
     </row>

--- a/grupos/6ARHM - Estadisticos 20232.xlsx
+++ b/grupos/6ARHM - Estadisticos 20232.xlsx
@@ -726,7 +726,7 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>10</v>
@@ -803,7 +803,7 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>10</v>
@@ -839,7 +839,7 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U5">
         <v>10</v>
@@ -880,7 +880,7 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>10</v>
@@ -957,7 +957,7 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>9</v>
@@ -1034,7 +1034,7 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>9</v>
@@ -1070,7 +1070,7 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1111,7 +1111,7 @@
         <v>6</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I9">
         <v>8</v>
@@ -1147,7 +1147,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U9">
         <v>9</v>
@@ -1188,7 +1188,7 @@
         <v>10</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I10">
         <v>8</v>
@@ -1224,7 +1224,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
         <v>9</v>
@@ -1265,7 +1265,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>10</v>
@@ -1342,7 +1342,7 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>10</v>
@@ -1378,7 +1378,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>10</v>
@@ -1419,7 +1419,7 @@
         <v>9</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>10</v>
@@ -1455,7 +1455,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1496,7 +1496,7 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>10</v>
@@ -1532,7 +1532,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>10</v>
@@ -1573,7 +1573,7 @@
         <v>10</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>10</v>
@@ -1650,7 +1650,7 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>9</v>
@@ -1686,7 +1686,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1727,7 +1727,7 @@
         <v>6</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <v>8</v>
@@ -1763,7 +1763,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -1804,7 +1804,7 @@
         <v>10</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>10</v>
@@ -1881,7 +1881,7 @@
         <v>9</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
         <v>10</v>
@@ -1958,7 +1958,7 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>10</v>
@@ -2035,7 +2035,7 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
         <v>9</v>
@@ -2112,7 +2112,7 @@
         <v>8</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I22">
         <v>8</v>
@@ -2148,7 +2148,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U22">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>9</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>9</v>
@@ -2225,7 +2225,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
         <v>9</v>
@@ -2266,7 +2266,7 @@
         <v>7</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
         <v>10</v>
@@ -2302,7 +2302,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>9</v>
@@ -2343,7 +2343,7 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
         <v>10</v>
@@ -2379,7 +2379,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U25">
         <v>9</v>
@@ -2420,7 +2420,7 @@
         <v>10</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>10</v>
@@ -2497,7 +2497,7 @@
         <v>4</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>10</v>
@@ -2533,7 +2533,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U27">
         <v>10</v>
@@ -2574,7 +2574,7 @@
         <v>9</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>10</v>
@@ -2651,7 +2651,7 @@
         <v>7</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I29">
         <v>10</v>
@@ -2687,7 +2687,7 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>9</v>
@@ -2728,7 +2728,7 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>8</v>
@@ -2764,7 +2764,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>9</v>
@@ -2805,7 +2805,7 @@
         <v>9</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>10</v>
@@ -2841,7 +2841,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>10</v>
@@ -2882,7 +2882,7 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>10</v>
@@ -2959,7 +2959,7 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U33">
         <v>8</v>
@@ -3036,7 +3036,7 @@
         <v>6</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
         <v>10</v>
@@ -3072,7 +3072,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>9</v>
@@ -3459,7 +3459,7 @@
         <v>90</v>
       </c>
       <c r="H8">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I8">
         <v>100</v>
@@ -3477,7 +3477,7 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N8">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O8">
         <v>100</v>
@@ -3990,7 +3990,7 @@
         <v>86.7</v>
       </c>
       <c r="H17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I17">
         <v>100</v>
@@ -4008,7 +4008,7 @@
         <v>80</v>
       </c>
       <c r="N17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O17">
         <v>100</v>
@@ -4403,7 +4403,7 @@
         <v>96.7</v>
       </c>
       <c r="H24">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I24">
         <v>100</v>
@@ -4421,7 +4421,7 @@
         <v>94.5</v>
       </c>
       <c r="N24">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O24">
         <v>100</v>
@@ -4580,7 +4580,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -4598,7 +4598,7 @@
         <v>94.5</v>
       </c>
       <c r="N27">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -4993,7 +4993,7 @@
         <v>100</v>
       </c>
       <c r="H34">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I34">
         <v>100</v>
@@ -5011,7 +5011,7 @@
         <v>92.7</v>
       </c>
       <c r="N34">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -5136,7 +5136,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I3">
         <v>0</v>

--- a/grupos/6ARHM - Estadisticos 20232.xlsx
+++ b/grupos/6ARHM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="66">
   <si>
     <t>Materia</t>
   </si>
@@ -71,6 +71,9 @@
     <t>CERON COCOTLE LAURA EVELYN</t>
   </si>
   <si>
+    <t>CHAVEZ DE GANTE YARETZI VALERIA</t>
+  </si>
+  <si>
     <t>CHAVEZ SANCHEZ JESUS MANUEL</t>
   </si>
   <si>
@@ -107,6 +110,9 @@
     <t>MENDEZ MARTINEZ AMY</t>
   </si>
   <si>
+    <t>MONTERO LOPEZ MARIA DEL PILAR</t>
+  </si>
+  <si>
     <t>PEREZ MARES RAFAEL</t>
   </si>
   <si>
@@ -185,15 +191,15 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Martínez Marañon Mauricio</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Camacho Juárez Sergio Eduardo</t>
   </si>
   <si>
-    <t>Martínez Marañon Mauricio</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
     <t>Velasco Sánchez David</t>
   </si>
   <si>
@@ -210,15 +216,6 @@
   </si>
   <si>
     <t>Nombres</t>
-  </si>
-  <si>
-    <t>IXMATLAHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LIZBETH JOSELYN</t>
   </si>
 </sst>
 </file>
@@ -580,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y34"/>
+  <dimension ref="A1:Y36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -744,22 +741,22 @@
         <v>10</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -821,22 +818,22 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -898,22 +895,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -975,22 +972,22 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -999,7 +996,7 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1052,22 +1049,22 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1099,70 +1096,70 @@
         <v>9</v>
       </c>
       <c r="D9">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J9">
         <v>9</v>
       </c>
       <c r="K9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U9">
         <v>9</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>8</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1179,13 +1176,13 @@
         <v>7</v>
       </c>
       <c r="E10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H10">
         <v>10</v>
@@ -1206,22 +1203,22 @@
         <v>10</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>10</v>
@@ -1230,16 +1227,16 @@
         <v>9</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1247,31 +1244,31 @@
         <v>19</v>
       </c>
       <c r="B11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11">
         <v>9</v>
       </c>
       <c r="D11">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G11">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H11">
         <v>10</v>
       </c>
       <c r="I11">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>8</v>
@@ -1283,28 +1280,28 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>10</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>9</v>
@@ -1313,10 +1310,10 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1324,7 +1321,7 @@
         <v>20</v>
       </c>
       <c r="B12">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C12">
         <v>9</v>
@@ -1333,7 +1330,7 @@
         <v>9</v>
       </c>
       <c r="E12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12">
         <v>10</v>
@@ -1342,7 +1339,7 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>10</v>
@@ -1351,7 +1348,7 @@
         <v>8</v>
       </c>
       <c r="K12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L12">
         <v>9</v>
@@ -1360,25 +1357,25 @@
         <v>10</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
         <v>10</v>
@@ -1390,7 +1387,7 @@
         <v>9</v>
       </c>
       <c r="X12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y12">
         <v>9</v>
@@ -1401,34 +1398,34 @@
         <v>21</v>
       </c>
       <c r="B13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13">
         <v>9</v>
       </c>
       <c r="D13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F13">
         <v>10</v>
       </c>
       <c r="G13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I13">
         <v>10</v>
       </c>
       <c r="J13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>9</v>
@@ -1437,25 +1434,25 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1464,13 +1461,13 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>10</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1478,25 +1475,25 @@
         <v>22</v>
       </c>
       <c r="B14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14">
         <v>9</v>
       </c>
       <c r="D14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F14">
         <v>10</v>
       </c>
       <c r="G14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>10</v>
@@ -1505,49 +1502,49 @@
         <v>7</v>
       </c>
       <c r="K14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U14">
         <v>10</v>
       </c>
       <c r="V14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W14">
         <v>8</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1555,76 +1552,76 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15">
         <v>10</v>
       </c>
       <c r="G15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I15">
         <v>10</v>
       </c>
       <c r="J15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U15">
         <v>10</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1632,76 +1629,76 @@
         <v>24</v>
       </c>
       <c r="B16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H16">
         <v>10</v>
       </c>
       <c r="I16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T16">
         <v>10</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1709,31 +1706,31 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K17">
         <v>8</v>
@@ -1742,43 +1739,43 @@
         <v>6</v>
       </c>
       <c r="M17">
+        <v>9</v>
+      </c>
+      <c r="N17">
+        <v>10</v>
+      </c>
+      <c r="O17">
+        <v>8</v>
+      </c>
+      <c r="P17">
+        <v>5</v>
+      </c>
+      <c r="Q17">
+        <v>10</v>
+      </c>
+      <c r="R17">
         <v>6</v>
       </c>
-      <c r="N17">
-        <v>-1</v>
-      </c>
-      <c r="O17">
-        <v>-1</v>
-      </c>
-      <c r="P17">
-        <v>-1</v>
-      </c>
-      <c r="Q17">
-        <v>-1</v>
-      </c>
-      <c r="R17">
-        <v>-1</v>
-      </c>
       <c r="S17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X17">
         <v>7</v>
       </c>
       <c r="Y17">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1786,76 +1783,76 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E18">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J18">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1872,13 +1869,13 @@
         <v>9</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H19">
         <v>10</v>
@@ -1887,34 +1884,34 @@
         <v>10</v>
       </c>
       <c r="J19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M19">
         <v>10</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T19">
         <v>10</v>
@@ -1923,10 +1920,10 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -1943,19 +1940,19 @@
         <v>10</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F20">
         <v>10</v>
       </c>
       <c r="G20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H20">
         <v>10</v>
@@ -1967,31 +1964,31 @@
         <v>10</v>
       </c>
       <c r="K20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M20">
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2000,16 +1997,16 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2020,73 +2017,73 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D21">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H21">
         <v>10</v>
       </c>
       <c r="I21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T21">
         <v>10</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2094,76 +2091,76 @@
         <v>30</v>
       </c>
       <c r="B22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E22">
         <v>9</v>
       </c>
       <c r="F22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H22">
         <v>9</v>
       </c>
       <c r="I22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K22">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
         <v>9</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2171,16 +2168,16 @@
         <v>31</v>
       </c>
       <c r="B23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F23">
         <v>7</v>
@@ -2195,34 +2192,34 @@
         <v>9</v>
       </c>
       <c r="J23">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L23">
         <v>8</v>
       </c>
       <c r="M23">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>10</v>
@@ -2231,16 +2228,16 @@
         <v>9</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2254,70 +2251,70 @@
         <v>8</v>
       </c>
       <c r="D24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H24">
         <v>9</v>
       </c>
       <c r="I24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J24">
         <v>7</v>
       </c>
       <c r="K24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>9</v>
       </c>
       <c r="U24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y24">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2328,16 +2325,16 @@
         <v>9</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G25">
         <v>9</v>
@@ -2346,7 +2343,7 @@
         <v>10</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J25">
         <v>9</v>
@@ -2355,28 +2352,28 @@
         <v>8</v>
       </c>
       <c r="L25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M25">
         <v>10</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
@@ -2385,13 +2382,13 @@
         <v>9</v>
       </c>
       <c r="V25">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y25">
         <v>10</v>
@@ -2402,76 +2399,76 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C26">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I26">
         <v>10</v>
       </c>
       <c r="J26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2482,10 +2479,10 @@
         <v>9</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E27">
         <v>9</v>
@@ -2494,7 +2491,7 @@
         <v>10</v>
       </c>
       <c r="G27">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H27">
         <v>10</v>
@@ -2503,52 +2500,52 @@
         <v>10</v>
       </c>
       <c r="J27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L27">
         <v>9</v>
       </c>
       <c r="M27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V27">
         <v>9</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27">
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2571,7 +2568,7 @@
         <v>10</v>
       </c>
       <c r="G28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H28">
         <v>10</v>
@@ -2586,28 +2583,28 @@
         <v>10</v>
       </c>
       <c r="L28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M28">
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2633,64 +2630,64 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E29">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G29">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I29">
         <v>10</v>
       </c>
       <c r="J29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>8</v>
@@ -2699,10 +2696,10 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2710,73 +2707,73 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C30">
         <v>9</v>
       </c>
       <c r="D30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H30">
         <v>10</v>
       </c>
       <c r="I30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M30">
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
       </c>
       <c r="U30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y30">
         <v>10</v>
@@ -2787,76 +2784,76 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I31">
         <v>10</v>
       </c>
       <c r="J31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="M31">
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2864,19 +2861,19 @@
         <v>40</v>
       </c>
       <c r="B32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32">
         <v>9</v>
       </c>
       <c r="D32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E32">
         <v>9</v>
       </c>
       <c r="F32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G32">
         <v>10</v>
@@ -2885,52 +2882,52 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J32">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K32">
         <v>8</v>
       </c>
       <c r="L32">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>10</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
       </c>
       <c r="U32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>9</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -2941,76 +2938,76 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G33">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="K33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="M33">
         <v>10</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y33">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3018,76 +3015,230 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D34">
+        <v>9</v>
+      </c>
+      <c r="E34">
+        <v>9</v>
+      </c>
+      <c r="F34">
+        <v>10</v>
+      </c>
+      <c r="G34">
+        <v>10</v>
+      </c>
+      <c r="H34">
+        <v>10</v>
+      </c>
+      <c r="I34">
+        <v>10</v>
+      </c>
+      <c r="J34">
+        <v>9</v>
+      </c>
+      <c r="K34">
+        <v>8</v>
+      </c>
+      <c r="L34">
+        <v>9</v>
+      </c>
+      <c r="M34">
+        <v>10</v>
+      </c>
+      <c r="N34">
+        <v>10</v>
+      </c>
+      <c r="O34">
+        <v>10</v>
+      </c>
+      <c r="P34">
+        <v>10</v>
+      </c>
+      <c r="Q34">
+        <v>9</v>
+      </c>
+      <c r="R34">
+        <v>10</v>
+      </c>
+      <c r="S34">
+        <v>10</v>
+      </c>
+      <c r="T34">
+        <v>10</v>
+      </c>
+      <c r="U34">
+        <v>10</v>
+      </c>
+      <c r="V34">
+        <v>9</v>
+      </c>
+      <c r="W34">
+        <v>9</v>
+      </c>
+      <c r="X34">
+        <v>10</v>
+      </c>
+      <c r="Y34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35">
+        <v>8</v>
+      </c>
+      <c r="C35">
+        <v>8</v>
+      </c>
+      <c r="D35">
+        <v>7</v>
+      </c>
+      <c r="E35">
+        <v>9</v>
+      </c>
+      <c r="F35">
+        <v>7</v>
+      </c>
+      <c r="G35">
+        <v>7</v>
+      </c>
+      <c r="H35">
+        <v>9</v>
+      </c>
+      <c r="I35">
+        <v>8</v>
+      </c>
+      <c r="J35">
         <v>6</v>
       </c>
-      <c r="E34">
-        <v>8</v>
-      </c>
-      <c r="F34">
-        <v>7</v>
-      </c>
-      <c r="G34">
+      <c r="K35">
         <v>6</v>
       </c>
-      <c r="H34">
-        <v>9</v>
-      </c>
-      <c r="I34">
-        <v>10</v>
-      </c>
-      <c r="J34">
-        <v>7</v>
-      </c>
-      <c r="K34">
-        <v>9</v>
-      </c>
-      <c r="L34">
-        <v>7</v>
-      </c>
-      <c r="M34">
-        <v>8</v>
-      </c>
-      <c r="N34">
-        <v>-1</v>
-      </c>
-      <c r="O34">
-        <v>-1</v>
-      </c>
-      <c r="P34">
-        <v>-1</v>
-      </c>
-      <c r="Q34">
-        <v>-1</v>
-      </c>
-      <c r="R34">
-        <v>-1</v>
-      </c>
-      <c r="S34">
-        <v>-1</v>
-      </c>
-      <c r="T34">
-        <v>9</v>
-      </c>
-      <c r="U34">
-        <v>9</v>
-      </c>
-      <c r="V34">
-        <v>7</v>
-      </c>
-      <c r="W34">
-        <v>9</v>
-      </c>
-      <c r="X34">
-        <v>7</v>
-      </c>
-      <c r="Y34">
-        <v>7</v>
+      <c r="L35">
+        <v>5</v>
+      </c>
+      <c r="M35">
+        <v>10</v>
+      </c>
+      <c r="N35">
+        <v>10</v>
+      </c>
+      <c r="O35">
+        <v>9</v>
+      </c>
+      <c r="P35">
+        <v>8</v>
+      </c>
+      <c r="Q35">
+        <v>8</v>
+      </c>
+      <c r="R35">
+        <v>6</v>
+      </c>
+      <c r="S35">
+        <v>10</v>
+      </c>
+      <c r="T35">
+        <v>9</v>
+      </c>
+      <c r="U35">
+        <v>8</v>
+      </c>
+      <c r="V35">
+        <v>7</v>
+      </c>
+      <c r="W35">
+        <v>8</v>
+      </c>
+      <c r="X35">
+        <v>6</v>
+      </c>
+      <c r="Y35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25">
+      <c r="A36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36">
+        <v>8</v>
+      </c>
+      <c r="C36">
+        <v>8</v>
+      </c>
+      <c r="D36">
+        <v>6</v>
+      </c>
+      <c r="E36">
+        <v>8</v>
+      </c>
+      <c r="F36">
+        <v>7</v>
+      </c>
+      <c r="G36">
+        <v>6</v>
+      </c>
+      <c r="H36">
+        <v>9</v>
+      </c>
+      <c r="I36">
+        <v>10</v>
+      </c>
+      <c r="J36">
+        <v>7</v>
+      </c>
+      <c r="K36">
+        <v>9</v>
+      </c>
+      <c r="L36">
+        <v>7</v>
+      </c>
+      <c r="M36">
+        <v>8</v>
+      </c>
+      <c r="N36">
+        <v>10</v>
+      </c>
+      <c r="O36">
+        <v>10</v>
+      </c>
+      <c r="P36">
+        <v>6</v>
+      </c>
+      <c r="Q36">
+        <v>9</v>
+      </c>
+      <c r="R36">
+        <v>8</v>
+      </c>
+      <c r="S36">
+        <v>10</v>
+      </c>
+      <c r="T36">
+        <v>9</v>
+      </c>
+      <c r="U36">
+        <v>9</v>
+      </c>
+      <c r="V36">
+        <v>6</v>
+      </c>
+      <c r="W36">
+        <v>9</v>
+      </c>
+      <c r="X36">
+        <v>7</v>
+      </c>
+      <c r="Y36">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3103,7 +3254,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S34"/>
+  <dimension ref="A1:S36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -3112,7 +3263,7 @@
     <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -3120,7 +3271,7 @@
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -3128,7 +3279,7 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
@@ -3315,7 +3466,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3365,7 +3516,7 @@
         <v>100</v>
       </c>
       <c r="P6">
-        <v>98.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="Q6">
         <v>100</v>
@@ -3374,7 +3525,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>89.09999999999999</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3424,16 +3575,16 @@
         <v>100</v>
       </c>
       <c r="P7">
-        <v>92.3</v>
+        <v>95</v>
       </c>
       <c r="Q7">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R7">
-        <v>96.2</v>
+        <v>97.5</v>
       </c>
       <c r="S7">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3477,22 +3628,22 @@
         <v>90.90000000000001</v>
       </c>
       <c r="N8">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="O8">
         <v>100</v>
       </c>
       <c r="P8">
-        <v>98.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="Q8">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R8">
         <v>100</v>
       </c>
       <c r="S8">
-        <v>90.90000000000001</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -3506,16 +3657,16 @@
         <v>100</v>
       </c>
       <c r="D9">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>100</v>
       </c>
       <c r="F9">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="G9">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H9">
         <v>100</v>
@@ -3524,16 +3675,16 @@
         <v>100</v>
       </c>
       <c r="J9">
-        <v>96.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K9">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="L9">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="M9">
-        <v>83.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="N9">
         <v>100</v>
@@ -3542,16 +3693,16 @@
         <v>100</v>
       </c>
       <c r="P9">
-        <v>96.2</v>
+        <v>98.8</v>
       </c>
       <c r="Q9">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="R9">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="S9">
-        <v>83.59999999999999</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -3565,16 +3716,16 @@
         <v>100</v>
       </c>
       <c r="D10">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="E10">
         <v>100</v>
       </c>
       <c r="F10">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="G10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H10">
         <v>100</v>
@@ -3583,16 +3734,16 @@
         <v>100</v>
       </c>
       <c r="J10">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L10">
-        <v>98.09999999999999</v>
+        <v>96.2</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N10">
         <v>100</v>
@@ -3601,16 +3752,16 @@
         <v>100</v>
       </c>
       <c r="P10">
-        <v>92.3</v>
+        <v>97.5</v>
       </c>
       <c r="Q10">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R10">
-        <v>98.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>86.3</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -3624,7 +3775,7 @@
         <v>100</v>
       </c>
       <c r="D11">
-        <v>100</v>
+        <v>88.5</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -3633,7 +3784,7 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>100</v>
@@ -3642,16 +3793,16 @@
         <v>100</v>
       </c>
       <c r="J11">
-        <v>94.2</v>
+        <v>92.3</v>
       </c>
       <c r="K11">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="L11">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M11">
-        <v>94.5</v>
+        <v>100</v>
       </c>
       <c r="N11">
         <v>100</v>
@@ -3660,16 +3811,16 @@
         <v>100</v>
       </c>
       <c r="P11">
-        <v>94.2</v>
+        <v>95</v>
       </c>
       <c r="Q11">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S11">
-        <v>94.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -3692,7 +3843,7 @@
         <v>100</v>
       </c>
       <c r="G12">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H12">
         <v>100</v>
@@ -3707,10 +3858,10 @@
         <v>96.7</v>
       </c>
       <c r="L12">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="M12">
-        <v>96.40000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="N12">
         <v>100</v>
@@ -3719,16 +3870,16 @@
         <v>100</v>
       </c>
       <c r="P12">
-        <v>94.2</v>
+        <v>96.3</v>
       </c>
       <c r="Q12">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R12">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="S12">
-        <v>96.40000000000001</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -3760,13 +3911,13 @@
         <v>100</v>
       </c>
       <c r="J13">
-        <v>98.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="K13">
         <v>96.7</v>
       </c>
       <c r="L13">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M13">
         <v>96.40000000000001</v>
@@ -3778,16 +3929,16 @@
         <v>100</v>
       </c>
       <c r="P13">
-        <v>98.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="Q13">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R13">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S13">
-        <v>96.40000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -3801,34 +3952,34 @@
         <v>100</v>
       </c>
       <c r="D14">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="E14">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>100</v>
       </c>
       <c r="G14">
+        <v>100</v>
+      </c>
+      <c r="H14">
+        <v>100</v>
+      </c>
+      <c r="I14">
+        <v>100</v>
+      </c>
+      <c r="J14">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="K14">
         <v>96.7</v>
       </c>
-      <c r="H14">
-        <v>100</v>
-      </c>
-      <c r="I14">
-        <v>100</v>
-      </c>
-      <c r="J14">
-        <v>88.5</v>
-      </c>
-      <c r="K14">
-        <v>90</v>
-      </c>
       <c r="L14">
         <v>100</v>
       </c>
       <c r="M14">
-        <v>90.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N14">
         <v>100</v>
@@ -3837,16 +3988,16 @@
         <v>100</v>
       </c>
       <c r="P14">
-        <v>88.5</v>
+        <v>98.8</v>
       </c>
       <c r="Q14">
-        <v>90</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R14">
         <v>100</v>
       </c>
       <c r="S14">
-        <v>90.90000000000001</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -3860,16 +4011,16 @@
         <v>100</v>
       </c>
       <c r="D15">
-        <v>100</v>
+        <v>88.5</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="F15">
         <v>100</v>
       </c>
       <c r="G15">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H15">
         <v>100</v>
@@ -3878,16 +4029,16 @@
         <v>100</v>
       </c>
       <c r="J15">
-        <v>98.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="L15">
         <v>100</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N15">
         <v>100</v>
@@ -3896,16 +4047,16 @@
         <v>100</v>
       </c>
       <c r="P15">
-        <v>98.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="Q15">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R15">
         <v>100</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -3940,7 +4091,7 @@
         <v>98.09999999999999</v>
       </c>
       <c r="K16">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -3955,16 +4106,16 @@
         <v>100</v>
       </c>
       <c r="P16">
-        <v>98.09999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="Q16">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="R16">
         <v>100</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -3972,58 +4123,58 @@
         <v>25</v>
       </c>
       <c r="B17">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C17">
         <v>100</v>
       </c>
       <c r="D17">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="E17">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>100</v>
       </c>
       <c r="G17">
-        <v>86.7</v>
+        <v>100</v>
       </c>
       <c r="H17">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>100</v>
       </c>
       <c r="J17">
-        <v>92.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K17">
-        <v>90</v>
+        <v>96.7</v>
       </c>
       <c r="L17">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="M17">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="N17">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O17">
         <v>100</v>
       </c>
       <c r="P17">
-        <v>92.3</v>
+        <v>98.8</v>
       </c>
       <c r="Q17">
-        <v>90</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R17">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>80</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4031,58 +4182,58 @@
         <v>26</v>
       </c>
       <c r="B18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C18">
         <v>100</v>
       </c>
       <c r="D18">
-        <v>100</v>
+        <v>88.5</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="F18">
         <v>100</v>
       </c>
       <c r="G18">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="H18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I18">
         <v>100</v>
       </c>
       <c r="J18">
+        <v>92.3</v>
+      </c>
+      <c r="K18">
+        <v>90</v>
+      </c>
+      <c r="L18">
         <v>98.09999999999999</v>
       </c>
-      <c r="K18">
-        <v>100</v>
-      </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
       <c r="M18">
-        <v>96.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="N18">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O18">
         <v>100</v>
       </c>
       <c r="P18">
-        <v>98.09999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R18">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="S18">
-        <v>96.40000000000001</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4096,7 +4247,7 @@
         <v>100</v>
       </c>
       <c r="D19">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>100</v>
@@ -4114,16 +4265,16 @@
         <v>100</v>
       </c>
       <c r="J19">
-        <v>94.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K19">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
       </c>
       <c r="M19">
-        <v>100</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="N19">
         <v>100</v>
@@ -4132,16 +4283,16 @@
         <v>100</v>
       </c>
       <c r="P19">
-        <v>94.2</v>
+        <v>98.8</v>
       </c>
       <c r="Q19">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="R19">
         <v>100</v>
       </c>
       <c r="S19">
-        <v>100</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4155,7 +4306,7 @@
         <v>100</v>
       </c>
       <c r="D20">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="E20">
         <v>100</v>
@@ -4173,10 +4324,10 @@
         <v>100</v>
       </c>
       <c r="J20">
-        <v>98.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -4191,10 +4342,10 @@
         <v>100</v>
       </c>
       <c r="P20">
-        <v>98.09999999999999</v>
+        <v>95</v>
       </c>
       <c r="Q20">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -4214,10 +4365,10 @@
         <v>100</v>
       </c>
       <c r="D21">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="E21">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -4232,16 +4383,16 @@
         <v>100</v>
       </c>
       <c r="J21">
-        <v>92.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K21">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="L21">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="M21">
-        <v>92.7</v>
+        <v>100</v>
       </c>
       <c r="N21">
         <v>100</v>
@@ -4250,16 +4401,16 @@
         <v>100</v>
       </c>
       <c r="P21">
-        <v>92.3</v>
+        <v>98.8</v>
       </c>
       <c r="Q21">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="R21">
-        <v>96.2</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>92.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4273,16 +4424,16 @@
         <v>100</v>
       </c>
       <c r="D22">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>100</v>
       </c>
       <c r="F22">
-        <v>84.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="G22">
-        <v>83.3</v>
+        <v>100</v>
       </c>
       <c r="H22">
         <v>100</v>
@@ -4291,16 +4442,16 @@
         <v>100</v>
       </c>
       <c r="J22">
-        <v>86.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="K22">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="M22">
-        <v>87.3</v>
+        <v>100</v>
       </c>
       <c r="N22">
         <v>100</v>
@@ -4309,16 +4460,16 @@
         <v>100</v>
       </c>
       <c r="P22">
-        <v>86.5</v>
+        <v>98.8</v>
       </c>
       <c r="Q22">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="R22">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="S22">
-        <v>87.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4332,25 +4483,25 @@
         <v>100</v>
       </c>
       <c r="D23">
+        <v>88.5</v>
+      </c>
+      <c r="E23">
+        <v>93.3</v>
+      </c>
+      <c r="F23">
+        <v>100</v>
+      </c>
+      <c r="G23">
+        <v>100</v>
+      </c>
+      <c r="H23">
+        <v>100</v>
+      </c>
+      <c r="I23">
+        <v>100</v>
+      </c>
+      <c r="J23">
         <v>92.3</v>
-      </c>
-      <c r="E23">
-        <v>100</v>
-      </c>
-      <c r="F23">
-        <v>96.2</v>
-      </c>
-      <c r="G23">
-        <v>96.7</v>
-      </c>
-      <c r="H23">
-        <v>100</v>
-      </c>
-      <c r="I23">
-        <v>100</v>
-      </c>
-      <c r="J23">
-        <v>94.2</v>
       </c>
       <c r="K23">
         <v>93.3</v>
@@ -4359,7 +4510,7 @@
         <v>96.2</v>
       </c>
       <c r="M23">
-        <v>89.09999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="N23">
         <v>100</v>
@@ -4368,16 +4519,16 @@
         <v>100</v>
       </c>
       <c r="P23">
-        <v>94.2</v>
+        <v>95</v>
       </c>
       <c r="Q23">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="R23">
-        <v>96.2</v>
+        <v>97.5</v>
       </c>
       <c r="S23">
-        <v>89.09999999999999</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4385,58 +4536,58 @@
         <v>32</v>
       </c>
       <c r="B24">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C24">
         <v>100</v>
       </c>
       <c r="D24">
-        <v>96.2</v>
+        <v>88.5</v>
       </c>
       <c r="E24">
         <v>100</v>
       </c>
       <c r="F24">
-        <v>100</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="G24">
-        <v>96.7</v>
+        <v>83.3</v>
       </c>
       <c r="H24">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I24">
         <v>100</v>
       </c>
       <c r="J24">
-        <v>90.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="K24">
-        <v>96.7</v>
+        <v>93.3</v>
       </c>
       <c r="L24">
-        <v>100</v>
+        <v>88.5</v>
       </c>
       <c r="M24">
-        <v>94.5</v>
+        <v>87.3</v>
       </c>
       <c r="N24">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O24">
         <v>100</v>
       </c>
       <c r="P24">
-        <v>90.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="Q24">
-        <v>96.7</v>
+        <v>95.3</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>88.8</v>
       </c>
       <c r="S24">
-        <v>94.5</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4450,16 +4601,16 @@
         <v>100</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="E25">
         <v>100</v>
       </c>
       <c r="F25">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="G25">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H25">
         <v>100</v>
@@ -4468,16 +4619,16 @@
         <v>100</v>
       </c>
       <c r="J25">
-        <v>100</v>
+        <v>94.2</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="M25">
-        <v>100</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N25">
         <v>100</v>
@@ -4486,16 +4637,16 @@
         <v>100</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="Q25">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="R25">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>88.8</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -4503,13 +4654,13 @@
         <v>34</v>
       </c>
       <c r="B26">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
       <c r="D26">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="E26">
         <v>100</v>
@@ -4518,43 +4669,43 @@
         <v>100</v>
       </c>
       <c r="G26">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="H26">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I26">
         <v>100</v>
       </c>
       <c r="J26">
-        <v>100</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="L26">
         <v>100</v>
       </c>
       <c r="M26">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="N26">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O26">
         <v>100</v>
       </c>
       <c r="P26">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q26">
-        <v>100</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R26">
         <v>100</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4562,7 +4713,7 @@
         <v>35</v>
       </c>
       <c r="B27">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>100</v>
@@ -4580,7 +4731,7 @@
         <v>100</v>
       </c>
       <c r="H27">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I27">
         <v>100</v>
@@ -4589,16 +4740,16 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>100</v>
       </c>
       <c r="M27">
-        <v>94.5</v>
+        <v>100</v>
       </c>
       <c r="N27">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="O27">
         <v>100</v>
@@ -4607,13 +4758,13 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="R27">
         <v>100</v>
       </c>
       <c r="S27">
-        <v>94.5</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -4651,10 +4802,10 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="M28">
-        <v>94.5</v>
+        <v>100</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -4669,10 +4820,10 @@
         <v>100</v>
       </c>
       <c r="R28">
-        <v>98.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="S28">
-        <v>94.5</v>
+        <v>98.8</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -4680,58 +4831,58 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C29">
         <v>100</v>
       </c>
       <c r="D29">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="E29">
+        <v>100</v>
+      </c>
+      <c r="F29">
+        <v>100</v>
+      </c>
+      <c r="G29">
+        <v>100</v>
+      </c>
+      <c r="H29">
+        <v>90</v>
+      </c>
+      <c r="I29">
+        <v>100</v>
+      </c>
+      <c r="J29">
+        <v>100</v>
+      </c>
+      <c r="K29">
         <v>93.3</v>
       </c>
-      <c r="F29">
-        <v>100</v>
-      </c>
-      <c r="G29">
-        <v>100</v>
-      </c>
-      <c r="H29">
-        <v>100</v>
-      </c>
-      <c r="I29">
-        <v>100</v>
-      </c>
-      <c r="J29">
-        <v>92.3</v>
-      </c>
-      <c r="K29">
-        <v>96.7</v>
-      </c>
       <c r="L29">
         <v>100</v>
       </c>
       <c r="M29">
-        <v>85.5</v>
+        <v>94.5</v>
       </c>
       <c r="N29">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="O29">
         <v>100</v>
       </c>
       <c r="P29">
-        <v>92.3</v>
+        <v>100</v>
       </c>
       <c r="Q29">
-        <v>96.7</v>
+        <v>95.3</v>
       </c>
       <c r="R29">
-        <v>100</v>
+        <v>96.3</v>
       </c>
       <c r="S29">
-        <v>85.5</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -4745,13 +4896,13 @@
         <v>100</v>
       </c>
       <c r="D30">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>100</v>
       </c>
       <c r="F30">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="G30">
         <v>100</v>
@@ -4763,16 +4914,16 @@
         <v>100</v>
       </c>
       <c r="J30">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="K30">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="L30">
-        <v>92.3</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>94.5</v>
       </c>
       <c r="N30">
         <v>100</v>
@@ -4781,16 +4932,16 @@
         <v>100</v>
       </c>
       <c r="P30">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="R30">
-        <v>92.3</v>
+        <v>98.8</v>
       </c>
       <c r="S30">
-        <v>100</v>
+        <v>96.3</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -4804,10 +4955,10 @@
         <v>100</v>
       </c>
       <c r="D31">
-        <v>100</v>
+        <v>88.5</v>
       </c>
       <c r="E31">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -4822,16 +4973,16 @@
         <v>100</v>
       </c>
       <c r="J31">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="K31">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31">
-        <v>100</v>
+        <v>85.5</v>
       </c>
       <c r="N31">
         <v>100</v>
@@ -4840,16 +4991,16 @@
         <v>100</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Q31">
-        <v>93.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R31">
         <v>100</v>
       </c>
       <c r="S31">
-        <v>100</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -4863,13 +5014,13 @@
         <v>100</v>
       </c>
       <c r="D32">
-        <v>92.3</v>
+        <v>88.5</v>
       </c>
       <c r="E32">
-        <v>93.3</v>
+        <v>100</v>
       </c>
       <c r="F32">
-        <v>100</v>
+        <v>88.5</v>
       </c>
       <c r="G32">
         <v>100</v>
@@ -4881,16 +5032,16 @@
         <v>100</v>
       </c>
       <c r="J32">
-        <v>96.2</v>
+        <v>94.2</v>
       </c>
       <c r="K32">
         <v>96.7</v>
       </c>
       <c r="L32">
-        <v>100</v>
+        <v>92.3</v>
       </c>
       <c r="M32">
-        <v>94.5</v>
+        <v>100</v>
       </c>
       <c r="N32">
         <v>100</v>
@@ -4899,16 +5050,16 @@
         <v>100</v>
       </c>
       <c r="P32">
-        <v>96.2</v>
+        <v>96.3</v>
       </c>
       <c r="Q32">
-        <v>96.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R32">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="S32">
-        <v>94.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -4922,10 +5073,10 @@
         <v>100</v>
       </c>
       <c r="D33">
-        <v>88.5</v>
+        <v>100</v>
       </c>
       <c r="E33">
-        <v>100</v>
+        <v>86.7</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -4940,16 +5091,16 @@
         <v>100</v>
       </c>
       <c r="J33">
-        <v>84.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="K33">
         <v>93.3</v>
       </c>
       <c r="L33">
-        <v>86.5</v>
+        <v>100</v>
       </c>
       <c r="M33">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="N33">
         <v>100</v>
@@ -4958,16 +5109,16 @@
         <v>100</v>
       </c>
       <c r="P33">
-        <v>84.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="Q33">
-        <v>93.3</v>
+        <v>95.3</v>
       </c>
       <c r="R33">
-        <v>86.5</v>
+        <v>100</v>
       </c>
       <c r="S33">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -4975,7 +5126,7 @@
         <v>42</v>
       </c>
       <c r="B34">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>100</v>
@@ -4984,7 +5135,7 @@
         <v>92.3</v>
       </c>
       <c r="E34">
-        <v>100</v>
+        <v>93.3</v>
       </c>
       <c r="F34">
         <v>100</v>
@@ -4993,40 +5144,158 @@
         <v>100</v>
       </c>
       <c r="H34">
+        <v>100</v>
+      </c>
+      <c r="I34">
+        <v>100</v>
+      </c>
+      <c r="J34">
+        <v>96.2</v>
+      </c>
+      <c r="K34">
+        <v>96.7</v>
+      </c>
+      <c r="L34">
+        <v>100</v>
+      </c>
+      <c r="M34">
+        <v>94.5</v>
+      </c>
+      <c r="N34">
+        <v>100</v>
+      </c>
+      <c r="O34">
+        <v>100</v>
+      </c>
+      <c r="P34">
+        <v>97.5</v>
+      </c>
+      <c r="Q34">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="R34">
+        <v>100</v>
+      </c>
+      <c r="S34">
+        <v>96.3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35">
+        <v>100</v>
+      </c>
+      <c r="C35">
+        <v>100</v>
+      </c>
+      <c r="D35">
+        <v>88.5</v>
+      </c>
+      <c r="E35">
+        <v>100</v>
+      </c>
+      <c r="F35">
+        <v>100</v>
+      </c>
+      <c r="G35">
+        <v>100</v>
+      </c>
+      <c r="H35">
+        <v>100</v>
+      </c>
+      <c r="I35">
+        <v>100</v>
+      </c>
+      <c r="J35">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="K35">
+        <v>93.3</v>
+      </c>
+      <c r="L35">
+        <v>86.5</v>
+      </c>
+      <c r="M35">
+        <v>90.90000000000001</v>
+      </c>
+      <c r="N35">
+        <v>100</v>
+      </c>
+      <c r="O35">
+        <v>100</v>
+      </c>
+      <c r="P35">
+        <v>86.3</v>
+      </c>
+      <c r="Q35">
+        <v>95.3</v>
+      </c>
+      <c r="R35">
+        <v>91.3</v>
+      </c>
+      <c r="S35">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19">
+      <c r="A36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36">
+        <v>80</v>
+      </c>
+      <c r="C36">
+        <v>100</v>
+      </c>
+      <c r="D36">
+        <v>92.3</v>
+      </c>
+      <c r="E36">
+        <v>100</v>
+      </c>
+      <c r="F36">
+        <v>100</v>
+      </c>
+      <c r="G36">
+        <v>100</v>
+      </c>
+      <c r="H36">
         <v>90</v>
       </c>
-      <c r="I34">
-        <v>100</v>
-      </c>
-      <c r="J34">
+      <c r="I36">
+        <v>100</v>
+      </c>
+      <c r="J36">
         <v>94.2</v>
       </c>
-      <c r="K34">
-        <v>100</v>
-      </c>
-      <c r="L34">
-        <v>100</v>
-      </c>
-      <c r="M34">
+      <c r="K36">
+        <v>100</v>
+      </c>
+      <c r="L36">
+        <v>100</v>
+      </c>
+      <c r="M36">
         <v>92.7</v>
       </c>
-      <c r="N34">
-        <v>90</v>
-      </c>
-      <c r="O34">
-        <v>100</v>
-      </c>
-      <c r="P34">
-        <v>94.2</v>
-      </c>
-      <c r="Q34">
-        <v>100</v>
-      </c>
-      <c r="R34">
-        <v>100</v>
-      </c>
-      <c r="S34">
-        <v>92.7</v>
+      <c r="N36">
+        <v>93.8</v>
+      </c>
+      <c r="O36">
+        <v>100</v>
+      </c>
+      <c r="P36">
+        <v>96.3</v>
+      </c>
+      <c r="Q36">
+        <v>100</v>
+      </c>
+      <c r="R36">
+        <v>100</v>
+      </c>
+      <c r="S36">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -5054,57 +5323,57 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="2">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="G2" s="2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5115,16 +5384,16 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -5136,7 +5405,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5147,16 +5416,16 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -5168,7 +5437,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5182,13 +5451,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -5214,13 +5483,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5232,7 +5501,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5246,13 +5515,13 @@
         <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -5264,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5289,16 +5558,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -5314,7 +5583,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5323,48 +5592,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920235</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
